--- a/KatalonData/RADTestData/FEINmismatch.xlsx
+++ b/KatalonData/RADTestData/FEINmismatch.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{9CBBFBDF-61C2-4D84-ADD9-3049F95E8824}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{BD42B4DF-939D-4658-A211-2483A7F1FB00}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="15840" windowWidth="29040" xWindow="28680" xr2:uid="{7FA755C6-479D-490F-B3D9-5A283DD51A2C}" yWindow="-3945"/>
+    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{7FA755C6-479D-490F-B3D9-5A283DD51A2C}" yWindow="2952"/>
   </bookViews>
   <sheets>
     <sheet name="FEINmismatch" r:id="rId1" sheetId="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="138">
   <si>
     <t>Result</t>
   </si>
@@ -135,331 +135,322 @@
     <t>PTE Composite</t>
   </si>
   <si>
-    <t>Mon Feb 24 21:35:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:37:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:38:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:39:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:41:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:42:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:43:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:44:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:44:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:45:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:45:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:45:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:45:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:46:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:48:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:49:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:50:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:50:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:51:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:51:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:51:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:51:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:51:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:51:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:52:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:52:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:52:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:53:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:54:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:54:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:54:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:54:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:55:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:55:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:55:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:55:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:55:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:56:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:56:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:56:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:56:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:56:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:57:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:57:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:57:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:57:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:57:49 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 21:58:00 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 21:58:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:58:23 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 21:58:35 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 21:58:46 EST 2025</t>
-  </si>
-  <si>
     <t>DoNotRun</t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:02:34 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:03:45 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:04:55 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:06:06 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:06:12 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:06:18 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:06:24 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:06:29 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:06:35 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:07:45 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:08:56 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:10:04 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:11:14 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:11:20 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:11:26 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:11:32 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:11:38 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:11:44 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:11:50 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:11:56 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:12:01 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:12:07 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:13:20 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:14:32 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:18:18 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:18:24 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:18:30 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:18:36 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:18:41 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:18:47 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:18:53 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:18:59 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:19:04 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:20:17 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:21:29 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:22:42 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:23:55 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:25:08 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:25:14 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:25:20 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:25:25 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:25:31 EDT 2025</t>
+  </si>
+  <si>
+    <t>Sat Oct 04 15:25:37 EDT 2025</t>
+  </si>
+  <si>
+    <t>Wed Nov 05 11:24:43 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Nov 05 11:25:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Thu May 14 14:09:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 15:16:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 15:16:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:23:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:29:53 EDT 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Sat Oct 04 14:57:57 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 14:59:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:00:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:01:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:02:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:03:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:04:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:07:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:08:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:10:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:12:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:12:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:13:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:14:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:15:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:16:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:19:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:20:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:21:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:22:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:23:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:22:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:23:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:24:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:25:55 EST 2025</t>
+    <t>Thu May 21 22:36:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:37:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:37:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:37:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:37:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:37:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:37:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:38:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:38:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:38:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:38:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:38:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:38:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:39:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:39:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:39:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:39:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:39:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:40:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:40:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:40:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:40:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:40:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:40:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:40:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:41:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:41:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:41:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:41:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:41:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:41:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:42:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:42:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:42:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:42:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:42:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:42:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:43:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:43:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:43:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:43:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:43:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:43:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:43:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:44:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:44:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:44:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:44:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:44:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:44:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:45:06 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -830,18 +821,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4607C70C-95F5-42E8-8763-F94D5F6C9468}">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
     <col min="4" max="4" customWidth="true" style="1" width="48.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="43.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,12 +849,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>87</v>
-      </c>
-      <c r="B2" t="s">
-        <v>137</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -875,12 +866,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -892,12 +883,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -909,12 +900,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -926,9 +917,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>91</v>
@@ -943,7 +934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -960,9 +951,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>93</v>
@@ -977,9 +968,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>94</v>
@@ -994,9 +985,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>95</v>
@@ -1011,9 +1002,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>96</v>
@@ -1028,9 +1019,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>97</v>
@@ -1045,9 +1036,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
         <v>98</v>
@@ -1062,9 +1053,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>99</v>
@@ -1079,7 +1070,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1096,7 +1087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1113,9 +1104,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
         <v>102</v>
@@ -1130,9 +1121,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>103</v>
@@ -1147,9 +1138,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
         <v>104</v>
@@ -1164,9 +1155,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
         <v>105</v>
@@ -1181,9 +1172,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
         <v>106</v>
@@ -1198,9 +1189,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
         <v>107</v>
@@ -1215,9 +1206,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
         <v>108</v>
@@ -1232,9 +1223,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
         <v>109</v>
@@ -1249,9 +1240,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
         <v>110</v>
@@ -1266,9 +1257,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
         <v>111</v>
@@ -1283,9 +1274,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
         <v>112</v>
@@ -1300,9 +1291,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
         <v>113</v>
@@ -1317,9 +1308,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
         <v>114</v>
@@ -1331,6 +1322,23 @@
         <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1345,17 +1353,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834489CB-2884-4184-82EB-D42CF0009FC1}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.7265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="47.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="43.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="47.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1372,12 +1380,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -1389,12 +1397,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1406,12 +1414,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -1423,12 +1431,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -1440,12 +1448,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -1457,12 +1465,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -1474,12 +1482,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -1491,12 +1499,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -1508,12 +1516,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -1525,12 +1533,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1542,12 +1550,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1559,12 +1567,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1576,12 +1584,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1593,12 +1601,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1610,12 +1618,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1627,12 +1635,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1644,12 +1652,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1661,12 +1669,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1678,12 +1686,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1695,15 +1703,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>29</v>
@@ -1712,12 +1720,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1729,12 +1737,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1746,15 +1754,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>7</v>
@@ -1763,12 +1771,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>

--- a/KatalonData/RADTestData/FEINmismatch.xlsx
+++ b/KatalonData/RADTestData/FEINmismatch.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{BD42B4DF-939D-4658-A211-2483A7F1FB00}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D4D920-0B27-4252-A6A8-3441F84C9D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="16776" windowWidth="30936" xWindow="45972" xr2:uid="{7FA755C6-479D-490F-B3D9-5A283DD51A2C}" yWindow="2952"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{7FA755C6-479D-490F-B3D9-5A283DD51A2C}"/>
   </bookViews>
   <sheets>
-    <sheet name="FEINmismatch" r:id="rId1" sheetId="1"/>
-    <sheet name="FEINSSNmismatch" r:id="rId2" sheetId="2"/>
+    <sheet name="FEINmismatch" sheetId="1" r:id="rId1"/>
+    <sheet name="FEINSSNmismatch" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="134">
   <si>
     <t>Result</t>
   </si>
@@ -135,322 +135,310 @@
     <t>PTE Composite</t>
   </si>
   <si>
-    <t>Mon Feb 24 21:58:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 21:58:35 EST 2025</t>
-  </si>
-  <si>
     <t>DoNotRun</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:02:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:03:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:04:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:06:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:07:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:08:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:10:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:44 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:11:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:12:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:12:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:13:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:14:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:47 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:18:59 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:19:04 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:20:17 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:21:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:22:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:23:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:14 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:20 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 15:25:37 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:24:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:25:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu May 14 14:09:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 15:16:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 15:16:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:23:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:29:53 EDT 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thu May 21 22:36:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:37:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:37:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:37:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:37:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:37:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:37:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:38:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:38:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:38:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:38:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:38:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:38:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:39:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:39:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:39:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:39:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:39:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:40:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:40:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:40:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:40:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:40:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:40:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:40:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:41:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:41:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:41:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:41:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:41:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:41:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:42:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:42:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:42:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:42:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:42:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:42:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:43:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:43:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:43:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:43:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:43:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:43:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:43:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:44:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:44:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:44:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:44:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:44:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:44:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:45:06 EDT 2026</t>
+    <t>Wed Jun 24 23:50:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:50:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:50:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:50:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:51:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:51:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:51:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:51:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:51:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:51:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:51:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:52:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:52:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:52:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:52:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:52:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:52:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:52:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:53:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:53:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:53:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:53:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:53:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:53:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:54:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:54:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:54:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:58:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:58:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:59:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:59:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:59:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:59:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:59:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:59:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:59:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:00:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:00:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:00:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:00:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:00:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:00:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:00:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:01:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:01:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:01:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:01:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:41:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:43:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 20:43:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:47:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:48:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:48:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:48:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:48:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:48:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:48:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:49:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:49:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:49:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:49:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:49:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:49:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:49:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:50:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:50:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:50:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:50:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:50:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:50:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:50:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:50:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:51:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:51:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:51:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:51:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:51:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:51:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:51:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:52:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:56:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:56:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:56:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:57:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:57:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:57:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:57:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:57:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:57:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:58:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:58:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:58:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:58:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:58:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:58:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:58:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:59:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:59:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:59:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:59:28 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -500,19 +488,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -529,10 +517,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -567,7 +555,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -619,7 +607,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -730,21 +718,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -761,7 +749,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -813,15 +801,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4607C70C-95F5-42E8-8763-F94D5F6C9468}">
-  <dimension ref="A1:F30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4607C70C-95F5-42E8-8763-F94D5F6C9468}">
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -850,11 +838,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -867,11 +855,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>88</v>
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -884,11 +872,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>89</v>
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -901,11 +889,11 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -918,11 +906,11 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>91</v>
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -935,11 +923,11 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>92</v>
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -952,11 +940,11 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>93</v>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -969,11 +957,11 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>94</v>
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -986,11 +974,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>95</v>
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -1003,11 +991,11 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>96</v>
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1020,11 +1008,11 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1037,11 +1025,11 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1054,11 +1042,11 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>99</v>
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1071,11 +1059,11 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1088,11 +1076,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>101</v>
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1105,11 +1093,11 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>102</v>
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1122,11 +1110,11 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>103</v>
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1139,11 +1127,11 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>104</v>
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1156,11 +1144,11 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>105</v>
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1173,11 +1161,11 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>106</v>
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1190,11 +1178,11 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>107</v>
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1207,11 +1195,11 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>108</v>
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1224,11 +1212,11 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>109</v>
+      <c r="A24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -1241,11 +1229,11 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>110</v>
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1258,11 +1246,11 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>111</v>
+      <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1275,11 +1263,11 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" t="s">
-        <v>112</v>
+      <c r="A27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1292,11 +1280,11 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
-        <v>113</v>
+      <c r="A28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1309,11 +1297,11 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>114</v>
+      <c r="A29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1326,11 +1314,11 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" t="s">
-        <v>115</v>
+      <c r="A30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1342,8 +1330,25 @@
         <v>30</v>
       </c>
     </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1351,8 +1356,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834489CB-2884-4184-82EB-D42CF0009FC1}">
-  <dimension ref="A1:F25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834489CB-2884-4184-82EB-D42CF0009FC1}">
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
@@ -1381,11 +1386,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -1398,11 +1403,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1415,11 +1420,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>118</v>
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -1432,11 +1437,11 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>119</v>
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -1449,11 +1454,11 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>120</v>
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -1466,11 +1471,11 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>121</v>
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -1483,11 +1488,11 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>122</v>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -1500,11 +1505,11 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>123</v>
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -1517,11 +1522,11 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>124</v>
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -1534,11 +1539,11 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>125</v>
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1551,11 +1556,11 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>126</v>
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1568,11 +1573,11 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>127</v>
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1585,11 +1590,11 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>128</v>
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1602,11 +1607,11 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>129</v>
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1619,11 +1624,11 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>130</v>
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1636,11 +1641,11 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>131</v>
+      <c r="A17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1653,11 +1658,11 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>132</v>
+      <c r="A18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1670,11 +1675,11 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>133</v>
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1687,11 +1692,11 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>134</v>
+      <c r="A20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1704,14 +1709,8 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>29</v>
@@ -1721,11 +1720,11 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>135</v>
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1738,14 +1737,8 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>136</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>29</v>
@@ -1755,14 +1748,8 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>7</v>
@@ -1772,14 +1759,8 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>137</v>
-      </c>
       <c r="C25" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>7</v>
@@ -1789,6 +1770,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/RADTestData/FEINmismatch.xlsx
+++ b/KatalonData/RADTestData/FEINmismatch.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D4D920-0B27-4252-A6A8-3441F84C9D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7F6711-0318-4DEF-A763-C2CF95659D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{7FA755C6-479D-490F-B3D9-5A283DD51A2C}"/>
+    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{7FA755C6-479D-490F-B3D9-5A283DD51A2C}"/>
   </bookViews>
   <sheets>
     <sheet name="FEINmismatch" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="85">
   <si>
     <t>Result</t>
   </si>
@@ -138,159 +138,9 @@
     <t>DoNotRun</t>
   </si>
   <si>
-    <t>Wed Jun 24 23:50:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:50:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:50:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:50:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:51:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:51:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:51:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:51:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:51:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:51:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:51:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:52:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:52:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:52:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:52:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:52:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:52:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:52:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:53:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:53:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:53:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:53:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:53:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:53:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:54:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:54:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:54:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:58:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:58:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:59:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:59:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:59:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:59:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:59:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:59:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Wed Jun 24 23:59:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:00:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:00:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:00:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:00:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:00:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:00:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:00:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:01:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:01:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:01:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:01:34 EDT 2026</t>
-  </si>
-  <si>
     <t>Motor Fuel Floor Tax</t>
   </si>
   <si>
-    <t>Thu Jul 09 20:41:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 20:43:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 20:43:45 EDT 2026</t>
-  </si>
-  <si>
     <t>Thu Jul 09 22:47:58 EDT 2026</t>
   </si>
   <si>
@@ -439,13 +289,15 @@
   </si>
   <si>
     <t>Thu Jul 09 22:59:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 19:24:04 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -812,12 +664,12 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="48.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="48" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -842,7 +694,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -859,7 +711,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -876,7 +728,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -893,7 +745,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -910,7 +762,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -927,7 +779,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -944,7 +796,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -961,7 +813,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -978,7 +830,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -995,7 +847,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1012,7 +864,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1029,7 +881,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1046,7 +898,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1063,7 +915,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1080,7 +932,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1097,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1114,7 +966,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1131,7 +983,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1148,7 +1000,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1165,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1182,7 +1034,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1199,7 +1051,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1216,7 +1068,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -1233,7 +1085,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1250,7 +1102,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1267,7 +1119,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1284,7 +1136,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1301,7 +1153,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1318,7 +1170,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1334,8 +1186,8 @@
       <c r="A31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B31" t="s" s="1">
-        <v>113</v>
+      <c r="B31" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
@@ -1344,7 +1196,7 @@
         <v>7</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1360,12 +1212,12 @@
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="47.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="47.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -1390,7 +1242,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -1407,7 +1259,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1424,7 +1276,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -1441,7 +1293,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -1458,7 +1310,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -1475,7 +1327,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -1492,7 +1344,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -1509,7 +1361,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -1526,7 +1378,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -1543,7 +1395,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1560,7 +1412,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1577,7 +1429,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1594,7 +1446,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1611,7 +1463,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1628,7 +1480,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1645,7 +1497,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1662,7 +1514,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1679,7 +1531,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1696,7 +1548,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1724,7 +1576,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1759,8 +1611,14 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
       <c r="C25" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>7</v>
